--- a/Module 8 Data/Cloud Training/Status of Learners/participant_status.xlsx
+++ b/Module 8 Data/Cloud Training/Status of Learners/participant_status.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amalitech-my.sharepoint.com/personal/ernest_kwisanga_amalitech_com/Documents/Desktop/Moodle Labs/Specilization/DEM08/Module 8 Data/Cloud Training/Status of Learners/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_6EC500E5F613C8264F2C4C9A2DDAF1F661044826" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B078738-4A2F-41FF-8CDB-8147606C528E}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -160,8 +166,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,13 +230,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -268,7 +282,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -302,6 +316,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -336,9 +351,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -511,11 +527,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -537,7 +557,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -548,7 +568,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -559,7 +579,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -570,7 +590,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -581,7 +601,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -592,7 +612,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -603,7 +623,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -614,7 +634,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -625,7 +645,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -636,7 +656,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -647,7 +667,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -658,7 +678,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -669,7 +689,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -680,7 +700,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -691,7 +711,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -702,7 +722,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -713,7 +733,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -724,7 +744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -735,7 +755,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -746,7 +766,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -757,7 +777,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -768,7 +788,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -779,7 +799,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -790,7 +810,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -801,7 +821,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -812,7 +832,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -823,7 +843,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -834,7 +854,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -845,7 +865,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -856,7 +876,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -867,7 +887,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -878,7 +898,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -889,7 +909,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -900,7 +920,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -911,7 +931,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -922,7 +942,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -933,7 +953,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -944,7 +964,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -955,7 +975,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -969,4 +989,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{2f70ad68-4eca-4ffe-ad9d-60bfae449e23}" enabled="1" method="Standard" siteId="{b20a8f4d-0d6a-4f2e-83a2-181c968f8882}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>